--- a/education_forms/015_student_interest_survey--education_forms.xlsx
+++ b/education_forms/015_student_interest_survey--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>school_year</t>
+          <t>school_year_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>School Year</t>
+          <t>School Year 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>school_year_2</t>
+          <t>school_year_2_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>School Year</t>
+          <t>School Year 2 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>School Time</t>
+          <t>School Time 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -941,8 +941,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -970,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'sports'}</t>
+          <t>sports</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Sports'}</t>
+          <t>Sports</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'arts'}</t>
+          <t>arts</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Arts'}</t>
+          <t>Arts</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'music'}</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Music'}</t>
+          <t>Music</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'clubs'}</t>
+          <t>clubs</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Clubs'}</t>
+          <t>Clubs</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'math'}</t>
+          <t>math</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Math'}</t>
+          <t>Math</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'science'}</t>
+          <t>science</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Science'}</t>
+          <t>Science</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'history'}</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'History'}</t>
+          <t>History</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'geography'}</t>
+          <t>geography</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Geography'}</t>
+          <t>Geography</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'improve_skills'}</t>
+          <t>improve_skills</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Improve skills'}</t>
+          <t>Improve skills</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'have_fun'}</t>
+          <t>have_fun</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Have fun'}</t>
+          <t>Have fun</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'learn_new_things'}</t>
+          <t>learn_new_things</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Learn new things'}</t>
+          <t>Learn new things</t>
         </is>
       </c>
     </row>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'get_grades'}</t>
+          <t>get_grades</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Get grades'}</t>
+          <t>Get grades</t>
         </is>
       </c>
     </row>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'activities'}</t>
+          <t>activities</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Activities'}</t>
+          <t>Activities</t>
         </is>
       </c>
     </row>
@@ -1259,80 +1259,80 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'lessons'}</t>
+          <t>lessons</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Lessons'}</t>
+          <t>Lessons</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>school_year_2_choices</t>
+          <t>school_year_2_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'summer'}</t>
+          <t>summer</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Summer'}</t>
+          <t>Summer</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>school_year_2_choices</t>
+          <t>school_year_2_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'fall'}</t>
+          <t>fall</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Fall'}</t>
+          <t>Fall</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>school_year_2_choices</t>
+          <t>school_year_2_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'winter'}</t>
+          <t>winter</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Winter'}</t>
+          <t>Winter</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>school_year_2_choices</t>
+          <t>school_year_2_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'spring'}</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Spring'}</t>
+          <t>Spring</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Morning'}</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -1361,12 +1361,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Afternoon'}</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
@@ -1378,12 +1378,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Evening'}</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
